--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430788</v>
       </c>
       <c r="B2" t="n">
-        <v>105099</v>
+        <v>105112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121430787</v>
       </c>
       <c r="B3" t="n">
-        <v>105099</v>
+        <v>105112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430788</v>
       </c>
       <c r="B2" t="n">
-        <v>105112</v>
+        <v>105113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121430787</v>
       </c>
       <c r="B3" t="n">
-        <v>105112</v>
+        <v>105113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430788</v>
+        <v>121430787</v>
       </c>
       <c r="B2" t="n">
-        <v>105113</v>
+        <v>105116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661508</v>
+        <v>661624</v>
       </c>
       <c r="R2" t="n">
-        <v>6630316</v>
+        <v>6630277</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430787</v>
+        <v>121430788</v>
       </c>
       <c r="B3" t="n">
-        <v>105113</v>
+        <v>105116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661624</v>
+        <v>661508</v>
       </c>
       <c r="R3" t="n">
-        <v>6630277</v>
+        <v>6630316</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430787</v>
       </c>
       <c r="B2" t="n">
-        <v>105116</v>
+        <v>105122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121430788</v>
       </c>
       <c r="B3" t="n">
-        <v>105116</v>
+        <v>105122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430787</v>
       </c>
       <c r="B2" t="n">
-        <v>105122</v>
+        <v>105123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121430788</v>
       </c>
       <c r="B3" t="n">
-        <v>105122</v>
+        <v>105123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430787</v>
+        <v>121430788</v>
       </c>
       <c r="B2" t="n">
         <v>105123</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661624</v>
+        <v>661508</v>
       </c>
       <c r="R2" t="n">
-        <v>6630277</v>
+        <v>6630316</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430788</v>
+        <v>121430787</v>
       </c>
       <c r="B3" t="n">
         <v>105123</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661508</v>
+        <v>661624</v>
       </c>
       <c r="R3" t="n">
-        <v>6630316</v>
+        <v>6630277</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43699-2023 artfynd.xlsx
+++ b/artfynd/A 43699-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Karolin Ring, Sara Janbrink</t>
+          <t>Sara Janbrink, Karolin Ring, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Karolin Ring, Sara Janbrink</t>
+          <t>Sara Janbrink, Karolin Ring, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
